--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/54.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/54.xlsx
@@ -426,13 +426,13 @@
         <v>-11.79493114439497</v>
       </c>
       <c r="E2">
-        <v>-19.38212622802356</v>
+        <v>-16.55921340980555</v>
       </c>
       <c r="F2">
-        <v>1.780304708929314</v>
+        <v>1.746750858911517</v>
       </c>
       <c r="G2">
-        <v>-16.02921935082425</v>
+        <v>-14.89634417189164</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.4622318633572</v>
       </c>
       <c r="E3">
-        <v>-19.20345092361811</v>
+        <v>-17.18031370379969</v>
       </c>
       <c r="F3">
-        <v>1.909102586186193</v>
+        <v>2.077705173882393</v>
       </c>
       <c r="G3">
-        <v>-15.26590681711439</v>
+        <v>-14.7749380215434</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.05520810356258</v>
       </c>
       <c r="E4">
-        <v>-19.39159139663285</v>
+        <v>-17.98381888596897</v>
       </c>
       <c r="F4">
-        <v>3.003631062444402</v>
+        <v>1.772677101884336</v>
       </c>
       <c r="G4">
-        <v>-14.52722535324939</v>
+        <v>-14.23971710515304</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.61570975970067</v>
       </c>
       <c r="E5">
-        <v>-18.49474694314937</v>
+        <v>-18.44590517796939</v>
       </c>
       <c r="F5">
-        <v>3.057559437101455</v>
+        <v>1.910835530792849</v>
       </c>
       <c r="G5">
-        <v>-15.36330978169194</v>
+        <v>-13.87694370123948</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.15459940993373</v>
       </c>
       <c r="E6">
-        <v>-19.54020160425786</v>
+        <v>-18.85166146477116</v>
       </c>
       <c r="F6">
-        <v>2.870471002444381</v>
+        <v>2.310166604660407</v>
       </c>
       <c r="G6">
-        <v>-14.62053075419119</v>
+        <v>-13.69852280513821</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.677595831523588</v>
       </c>
       <c r="E7">
-        <v>-21.83572303560384</v>
+        <v>-19.46772806663961</v>
       </c>
       <c r="F7">
-        <v>1.896002784078321</v>
+        <v>2.216402041602725</v>
       </c>
       <c r="G7">
-        <v>-14.63002081077988</v>
+        <v>-13.31835923150325</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.196171532635789</v>
       </c>
       <c r="E8">
-        <v>-21.46761976267297</v>
+        <v>-19.94570454516882</v>
       </c>
       <c r="F8">
-        <v>3.003756974289627</v>
+        <v>2.295555860409829</v>
       </c>
       <c r="G8">
-        <v>-14.05962272176886</v>
+        <v>-13.23703192674548</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.717587262737277</v>
       </c>
       <c r="E9">
-        <v>-22.49468815724644</v>
+        <v>-20.28316957815644</v>
       </c>
       <c r="F9">
-        <v>2.262833691264443</v>
+        <v>2.372133456594227</v>
       </c>
       <c r="G9">
-        <v>-12.59156709850618</v>
+        <v>-12.42837337023257</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.232822335413008</v>
       </c>
       <c r="E10">
-        <v>-21.62883911988016</v>
+        <v>-21.79705663816969</v>
       </c>
       <c r="F10">
-        <v>2.313960527365229</v>
+        <v>2.435125827372712</v>
       </c>
       <c r="G10">
-        <v>-12.0749777608903</v>
+        <v>-12.26873547609206</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.753849801473856</v>
       </c>
       <c r="E11">
-        <v>-21.37671842640644</v>
+        <v>-21.89045820765376</v>
       </c>
       <c r="F11">
-        <v>3.821806232719862</v>
+        <v>2.634164290182572</v>
       </c>
       <c r="G11">
-        <v>-12.31201770529584</v>
+        <v>-11.5314220423928</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.282409156077129</v>
       </c>
       <c r="E12">
-        <v>-22.83327040408044</v>
+        <v>-22.00412329519167</v>
       </c>
       <c r="F12">
-        <v>3.228005970636287</v>
+        <v>2.765200416161814</v>
       </c>
       <c r="G12">
-        <v>-12.20956947679596</v>
+        <v>-11.22954947755615</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.812041095290687</v>
       </c>
       <c r="E13">
-        <v>-25.15946330106028</v>
+        <v>-23.26077705859034</v>
       </c>
       <c r="F13">
-        <v>3.478878695308923</v>
+        <v>2.971995711331489</v>
       </c>
       <c r="G13">
-        <v>-12.08816463182001</v>
+        <v>-10.30504304592948</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.355532246426893</v>
       </c>
       <c r="E14">
-        <v>-24.07830763540357</v>
+        <v>-24.59778715470179</v>
       </c>
       <c r="F14">
-        <v>3.923894231440873</v>
+        <v>3.302020598076423</v>
       </c>
       <c r="G14">
-        <v>-9.925153600476582</v>
+        <v>-10.16461762123497</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.910396534883307</v>
       </c>
       <c r="E15">
-        <v>-26.53860772606212</v>
+        <v>-24.93333755726866</v>
       </c>
       <c r="F15">
-        <v>2.957880330787785</v>
+        <v>3.281274964840712</v>
       </c>
       <c r="G15">
-        <v>-11.00594050869959</v>
+        <v>-9.89810889725724</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.469420707654066</v>
       </c>
       <c r="E16">
-        <v>-27.58734342411723</v>
+        <v>-25.5809685652058</v>
       </c>
       <c r="F16">
-        <v>3.501362243355707</v>
+        <v>3.624166054085928</v>
       </c>
       <c r="G16">
-        <v>-10.59805996511308</v>
+        <v>-9.134875991257408</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.037938250956755</v>
       </c>
       <c r="E17">
-        <v>-26.95356337594839</v>
+        <v>-26.80816775388879</v>
       </c>
       <c r="F17">
-        <v>3.920381953653003</v>
+        <v>3.838232758317377</v>
       </c>
       <c r="G17">
-        <v>-10.09829557101462</v>
+        <v>-9.081103790286544</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.607942265362825</v>
       </c>
       <c r="E18">
-        <v>-27.36974422317548</v>
+        <v>-26.60162855470507</v>
       </c>
       <c r="F18">
-        <v>4.468933474726058</v>
+        <v>4.11923320542983</v>
       </c>
       <c r="G18">
-        <v>-9.402276284513004</v>
+        <v>-8.420862147661541</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.17240923698402</v>
       </c>
       <c r="E19">
-        <v>-26.42995556459328</v>
+        <v>-27.18264620620328</v>
       </c>
       <c r="F19">
-        <v>3.874518564029606</v>
+        <v>4.121015852080655</v>
       </c>
       <c r="G19">
-        <v>-9.800315626363318</v>
+        <v>-8.088488253766908</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.735814888027152</v>
       </c>
       <c r="E20">
-        <v>-28.08075323592951</v>
+        <v>-28.76563231963337</v>
       </c>
       <c r="F20">
-        <v>4.96875545496203</v>
+        <v>4.482266876441519</v>
       </c>
       <c r="G20">
-        <v>-8.78556489182793</v>
+        <v>-8.059447636307659</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.29755174155955</v>
       </c>
       <c r="E21">
-        <v>-29.71868633518707</v>
+        <v>-29.03264435231226</v>
       </c>
       <c r="F21">
-        <v>5.454377561179212</v>
+        <v>4.521180263555428</v>
       </c>
       <c r="G21">
-        <v>-8.582007746803416</v>
+        <v>-7.724678384250681</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.864789156695181</v>
       </c>
       <c r="E22">
-        <v>-29.37798595057741</v>
+        <v>-29.47616163647937</v>
       </c>
       <c r="F22">
-        <v>5.09652118643502</v>
+        <v>4.672766528063321</v>
       </c>
       <c r="G22">
-        <v>-8.897334783890376</v>
+        <v>-7.654055132316476</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.453148764573029</v>
       </c>
       <c r="E23">
-        <v>-29.7623324329997</v>
+        <v>-29.28610237983257</v>
       </c>
       <c r="F23">
-        <v>4.934699614298136</v>
+        <v>4.568403832454223</v>
       </c>
       <c r="G23">
-        <v>-8.971912008507822</v>
+        <v>-7.380557445068334</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.073348160368852</v>
       </c>
       <c r="E24">
-        <v>-30.36127326797021</v>
+        <v>-30.29664306993889</v>
       </c>
       <c r="F24">
-        <v>4.480611798370726</v>
+        <v>4.859270135334019</v>
       </c>
       <c r="G24">
-        <v>-7.055812146868934</v>
+        <v>-7.176658292502387</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.740784786568039</v>
       </c>
       <c r="E25">
-        <v>-32.21065881540877</v>
+        <v>-31.14981650634179</v>
       </c>
       <c r="F25">
-        <v>5.218569526093888</v>
+        <v>4.839316421335385</v>
       </c>
       <c r="G25">
-        <v>-9.019743460161608</v>
+        <v>-7.193354004162556</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.471470138989366</v>
       </c>
       <c r="E26">
-        <v>-31.29563367935086</v>
+        <v>-30.4620550939785</v>
       </c>
       <c r="F26">
-        <v>5.325649266784168</v>
+        <v>4.811181750866702</v>
       </c>
       <c r="G26">
-        <v>-8.451800776438528</v>
+        <v>-7.014431845099789</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.271374179022349</v>
       </c>
       <c r="E27">
-        <v>-31.6325671012889</v>
+        <v>-30.13507276637475</v>
       </c>
       <c r="F27">
-        <v>4.768116586329961</v>
+        <v>4.666074976183507</v>
       </c>
       <c r="G27">
-        <v>-8.029823517432296</v>
+        <v>-7.139917283871649</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.146173005338013</v>
       </c>
       <c r="E28">
-        <v>-30.2268670430761</v>
+        <v>-30.78068946681934</v>
       </c>
       <c r="F28">
-        <v>4.847583528015323</v>
+        <v>4.889568501458814</v>
       </c>
       <c r="G28">
-        <v>-7.536262252482331</v>
+        <v>-6.749514369950342</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.098749306264631</v>
       </c>
       <c r="E29">
-        <v>-31.96442945219933</v>
+        <v>-31.29691286843891</v>
       </c>
       <c r="F29">
-        <v>4.682423635245158</v>
+        <v>4.714539439451695</v>
       </c>
       <c r="G29">
-        <v>-7.926084275732115</v>
+        <v>-6.864551608868567</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.123317528230512</v>
       </c>
       <c r="E30">
-        <v>-30.79673539877282</v>
+        <v>-30.09990544948176</v>
       </c>
       <c r="F30">
-        <v>5.305910928310262</v>
+        <v>4.53181815774218</v>
       </c>
       <c r="G30">
-        <v>-8.070146467642042</v>
+        <v>-7.071912608762331</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.213036674483145</v>
       </c>
       <c r="E31">
-        <v>-31.47965624333703</v>
+        <v>-30.32093312637215</v>
       </c>
       <c r="F31">
-        <v>4.503504559914493</v>
+        <v>4.703137790519563</v>
       </c>
       <c r="G31">
-        <v>-7.36823734134287</v>
+        <v>-6.833849252477075</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.358984447338109</v>
       </c>
       <c r="E32">
-        <v>-29.82986780235273</v>
+        <v>-29.87001897283551</v>
       </c>
       <c r="F32">
-        <v>4.56700057807388</v>
+        <v>4.46772074484836</v>
       </c>
       <c r="G32">
-        <v>-7.291434456961499</v>
+        <v>-6.97292622759027</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.545065181624093</v>
       </c>
       <c r="E33">
-        <v>-31.94292412395936</v>
+        <v>-30.41191129704818</v>
       </c>
       <c r="F33">
-        <v>4.850933445792244</v>
+        <v>4.519424124661493</v>
       </c>
       <c r="G33">
-        <v>-8.115482047466724</v>
+        <v>-6.771186160801173</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.75965473306243</v>
       </c>
       <c r="E34">
-        <v>-31.13871289586486</v>
+        <v>-29.86659880330952</v>
       </c>
       <c r="F34">
-        <v>5.367524895730489</v>
+        <v>4.491799728512936</v>
       </c>
       <c r="G34">
-        <v>-7.620791635481101</v>
+        <v>-7.080509790700867</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.992132224124143</v>
       </c>
       <c r="E35">
-        <v>-30.44563952621711</v>
+        <v>-29.75239587490504</v>
       </c>
       <c r="F35">
-        <v>4.766285894369775</v>
+        <v>4.417727115354604</v>
       </c>
       <c r="G35">
-        <v>-7.607235344191745</v>
+        <v>-7.131870969041838</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.229994390229796</v>
       </c>
       <c r="E36">
-        <v>-30.55349427111159</v>
+        <v>-29.25627816930897</v>
       </c>
       <c r="F36">
-        <v>4.770841915085172</v>
+        <v>4.602376836377836</v>
       </c>
       <c r="G36">
-        <v>-8.159168942082118</v>
+        <v>-7.109677029272784</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.466989792132526</v>
       </c>
       <c r="E37">
-        <v>-30.31318531064568</v>
+        <v>-29.25702990055877</v>
       </c>
       <c r="F37">
-        <v>5.258788420234609</v>
+        <v>4.615918986678802</v>
       </c>
       <c r="G37">
-        <v>-8.006671434398305</v>
+        <v>-7.514138802817237</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.699932582677255</v>
       </c>
       <c r="E38">
-        <v>-27.88762475611365</v>
+        <v>-28.98849571592933</v>
       </c>
       <c r="F38">
-        <v>4.996845393590961</v>
+        <v>4.796990160521941</v>
       </c>
       <c r="G38">
-        <v>-7.994695948958868</v>
+        <v>-7.252876370095348</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.923282862268523</v>
       </c>
       <c r="E39">
-        <v>-28.0385649152919</v>
+        <v>-27.99110201627176</v>
       </c>
       <c r="F39">
-        <v>5.120757559906128</v>
+        <v>5.021779252415226</v>
       </c>
       <c r="G39">
-        <v>-8.495956299708027</v>
+        <v>-7.718151522772898</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.14035157998623</v>
       </c>
       <c r="E40">
-        <v>-28.27735380041291</v>
+        <v>-27.68339474242654</v>
       </c>
       <c r="F40">
-        <v>4.863857634010722</v>
+        <v>4.929094880450795</v>
       </c>
       <c r="G40">
-        <v>-7.833669138695887</v>
+        <v>-7.617231885231118</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.356106855799359</v>
       </c>
       <c r="E41">
-        <v>-29.20256053403364</v>
+        <v>-27.934335923884</v>
       </c>
       <c r="F41">
-        <v>4.821476700948694</v>
+        <v>4.83370174707921</v>
       </c>
       <c r="G41">
-        <v>-8.419782604773115</v>
+        <v>-8.047589634374823</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.569896599898278</v>
       </c>
       <c r="E42">
-        <v>-27.47543514496972</v>
+        <v>-26.98344988464186</v>
       </c>
       <c r="F42">
-        <v>5.001126396328629</v>
+        <v>4.728210815067498</v>
       </c>
       <c r="G42">
-        <v>-9.062292070135276</v>
+        <v>-7.947199977985039</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.790903464343136</v>
       </c>
       <c r="E43">
-        <v>-27.42569213293225</v>
+        <v>-26.04472860137014</v>
       </c>
       <c r="F43">
-        <v>5.061486215501017</v>
+        <v>5.049382111011311</v>
       </c>
       <c r="G43">
-        <v>-8.857844661205196</v>
+        <v>-7.72030147094368</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.025139926905563</v>
       </c>
       <c r="E44">
-        <v>-26.6547938128742</v>
+        <v>-25.83942290594988</v>
       </c>
       <c r="F44">
-        <v>4.474990497175328</v>
+        <v>5.111397008254493</v>
       </c>
       <c r="G44">
-        <v>-8.897059350336013</v>
+        <v>-7.764013167632689</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.270802180385949</v>
       </c>
       <c r="E45">
-        <v>-26.10196815984892</v>
+        <v>-25.57787857598013</v>
       </c>
       <c r="F45">
-        <v>5.35788766936632</v>
+        <v>5.259043557394672</v>
       </c>
       <c r="G45">
-        <v>-9.200004931199617</v>
+        <v>-7.879387192603168</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.535686923276053</v>
       </c>
       <c r="E46">
-        <v>-24.87654654561296</v>
+        <v>-25.38741645783482</v>
       </c>
       <c r="F46">
-        <v>5.136973680183331</v>
+        <v>5.153887285813691</v>
       </c>
       <c r="G46">
-        <v>-9.385562297640698</v>
+        <v>-8.111665138874516</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.819886701831834</v>
       </c>
       <c r="E47">
-        <v>-27.28690842330178</v>
+        <v>-24.2699783380444</v>
       </c>
       <c r="F47">
-        <v>5.857646693679678</v>
+        <v>5.144655959476894</v>
       </c>
       <c r="G47">
-        <v>-8.734182827530228</v>
+        <v>-8.090219177430816</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.116428596337577</v>
       </c>
       <c r="E48">
-        <v>-25.77310858072635</v>
+        <v>-24.25292940555598</v>
       </c>
       <c r="F48">
-        <v>5.434589520661137</v>
+        <v>5.053008703500767</v>
       </c>
       <c r="G48">
-        <v>-9.012002602448957</v>
+        <v>-8.077662801319857</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.427783629494258</v>
       </c>
       <c r="E49">
-        <v>-23.39281595302929</v>
+        <v>-24.0472333082712</v>
       </c>
       <c r="F49">
-        <v>5.661913416806989</v>
+        <v>5.173836029607909</v>
       </c>
       <c r="G49">
-        <v>-9.368394041209536</v>
+        <v>-7.911632499048007</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.747395410589191</v>
       </c>
       <c r="E50">
-        <v>-23.23661367510249</v>
+        <v>-23.28698797526133</v>
       </c>
       <c r="F50">
-        <v>4.966270352753631</v>
+        <v>5.194881531843433</v>
       </c>
       <c r="G50">
-        <v>-9.134932122266118</v>
+        <v>-8.386089640452502</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.065681116696485</v>
       </c>
       <c r="E51">
-        <v>-23.40110160962232</v>
+        <v>-22.63142018048245</v>
       </c>
       <c r="F51">
-        <v>5.531415729639566</v>
+        <v>4.999661842760479</v>
       </c>
       <c r="G51">
-        <v>-8.88248878477301</v>
+        <v>-8.246944785979938</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.383427615556903</v>
       </c>
       <c r="E52">
-        <v>-23.34085512614436</v>
+        <v>-21.6843135635459</v>
       </c>
       <c r="F52">
-        <v>5.089390599831722</v>
+        <v>5.335047923336332</v>
       </c>
       <c r="G52">
-        <v>-9.648290663450496</v>
+        <v>-8.390440446313592</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.692765726569192</v>
       </c>
       <c r="E53">
-        <v>-23.30023256617621</v>
+        <v>-21.4612861154026</v>
       </c>
       <c r="F53">
-        <v>5.342584409967002</v>
+        <v>5.180378475355219</v>
       </c>
       <c r="G53">
-        <v>-8.525387223483648</v>
+        <v>-8.545881568523887</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.987796173510416</v>
       </c>
       <c r="E54">
-        <v>-22.40698064048871</v>
+        <v>-21.38848447408968</v>
       </c>
       <c r="F54">
-        <v>4.785033505429933</v>
+        <v>4.942925302607936</v>
       </c>
       <c r="G54">
-        <v>-8.921666923479551</v>
+        <v>-8.857278129628924</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.271630549612993</v>
       </c>
       <c r="E55">
-        <v>-21.00434980544497</v>
+        <v>-20.63179013676255</v>
       </c>
       <c r="F55">
-        <v>5.16330250971391</v>
+        <v>5.291699457147834</v>
       </c>
       <c r="G55">
-        <v>-9.296079026780289</v>
+        <v>-8.536707412030715</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.53775683734871</v>
       </c>
       <c r="E56">
-        <v>-22.26063808624705</v>
+        <v>-20.76607176531691</v>
       </c>
       <c r="F56">
-        <v>4.961687824281344</v>
+        <v>5.026504260080794</v>
       </c>
       <c r="G56">
-        <v>-9.53466714272836</v>
+        <v>-9.016812899358083</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.78592415329324</v>
       </c>
       <c r="E57">
-        <v>-21.11710949291406</v>
+        <v>-19.01609125433245</v>
       </c>
       <c r="F57">
-        <v>4.561642697712573</v>
+        <v>5.034821068804901</v>
       </c>
       <c r="G57">
-        <v>-9.367497250442488</v>
+        <v>-9.1875830084351</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.022390960216635</v>
       </c>
       <c r="E58">
-        <v>-19.19501990462871</v>
+        <v>-19.42963481236828</v>
       </c>
       <c r="F58">
-        <v>5.410866734979765</v>
+        <v>4.928581292661059</v>
       </c>
       <c r="G58">
-        <v>-9.715959857879858</v>
+        <v>-8.671745565261459</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.242098720556925</v>
       </c>
       <c r="E59">
-        <v>-20.46555785348628</v>
+        <v>-19.2788234027411</v>
       </c>
       <c r="F59">
-        <v>4.925455034082894</v>
+        <v>4.985513327520664</v>
       </c>
       <c r="G59">
-        <v>-10.09883338440039</v>
+        <v>-8.846111975012732</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.450967774167303</v>
       </c>
       <c r="E60">
-        <v>-19.08361416405151</v>
+        <v>-18.86160840589413</v>
       </c>
       <c r="F60">
-        <v>4.577534097967879</v>
+        <v>5.058359956922852</v>
       </c>
       <c r="G60">
-        <v>-9.400515337286299</v>
+        <v>-9.186630086659342</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.656590327217291</v>
       </c>
       <c r="E61">
-        <v>-20.61303423441962</v>
+        <v>-18.58095099740751</v>
       </c>
       <c r="F61">
-        <v>4.51234489683717</v>
+        <v>4.57500757738934</v>
       </c>
       <c r="G61">
-        <v>-8.48884593681413</v>
+        <v>-9.294682278424045</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.851913003605722</v>
       </c>
       <c r="E62">
-        <v>-19.86829283928534</v>
+        <v>-17.88958252100861</v>
       </c>
       <c r="F62">
-        <v>4.518425113573717</v>
+        <v>4.682534636477134</v>
       </c>
       <c r="G62">
-        <v>-10.07006036826173</v>
+        <v>-9.126445896972704</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.044796390997156</v>
       </c>
       <c r="E63">
-        <v>-19.03887992487178</v>
+        <v>-17.54272707721555</v>
       </c>
       <c r="F63">
-        <v>4.642496326430222</v>
+        <v>4.643082810551404</v>
       </c>
       <c r="G63">
-        <v>-10.24255226339659</v>
+        <v>-9.314432561255815</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.238337249400969</v>
       </c>
       <c r="E64">
-        <v>-19.64774485830297</v>
+        <v>-17.56356789164354</v>
       </c>
       <c r="F64">
-        <v>4.587464566392639</v>
+        <v>4.501869362661367</v>
       </c>
       <c r="G64">
-        <v>-11.46973928531087</v>
+        <v>-9.386207151554702</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.420881593371073</v>
       </c>
       <c r="E65">
-        <v>-18.58618819688812</v>
+        <v>-16.82368990697064</v>
       </c>
       <c r="F65">
-        <v>4.478772822736511</v>
+        <v>4.389560966924615</v>
       </c>
       <c r="G65">
-        <v>-10.52691064814376</v>
+        <v>-9.73036594653362</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.600390838048149</v>
       </c>
       <c r="E66">
-        <v>-18.91946263964899</v>
+        <v>-16.72864781901326</v>
       </c>
       <c r="F66">
-        <v>4.23531398631893</v>
+        <v>4.541806611885137</v>
       </c>
       <c r="G66">
-        <v>-9.445679913340262</v>
+        <v>-9.657547058398288</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.77619301865605</v>
       </c>
       <c r="E67">
-        <v>-18.71267424778577</v>
+        <v>-16.67157023577614</v>
       </c>
       <c r="F67">
-        <v>4.650140500823256</v>
+        <v>4.195558977923777</v>
       </c>
       <c r="G67">
-        <v>-10.84483145998199</v>
+        <v>-9.435349196993227</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.935548989612412</v>
       </c>
       <c r="E68">
-        <v>-17.79551228450124</v>
+        <v>-16.5017952632398</v>
       </c>
       <c r="F68">
-        <v>3.977186419932576</v>
+        <v>4.299041947351102</v>
       </c>
       <c r="G68">
-        <v>-10.41492667502484</v>
+        <v>-9.514133636519253</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.08797887717201</v>
       </c>
       <c r="E69">
-        <v>-17.5451940847425</v>
+        <v>-16.16354112010046</v>
       </c>
       <c r="F69">
-        <v>5.159220315152914</v>
+        <v>4.433383259267515</v>
       </c>
       <c r="G69">
-        <v>-10.45030487497902</v>
+        <v>-9.726263161408685</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.2297059012418</v>
       </c>
       <c r="E70">
-        <v>-16.69936352596189</v>
+        <v>-16.65805983933647</v>
       </c>
       <c r="F70">
-        <v>3.996040062020293</v>
+        <v>4.355228451548187</v>
       </c>
       <c r="G70">
-        <v>-11.73476902247773</v>
+        <v>-9.839203972420247</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.34871441260777</v>
       </c>
       <c r="E71">
-        <v>-16.63280831448152</v>
+        <v>-16.23098927201568</v>
       </c>
       <c r="F71">
-        <v>5.101239567161366</v>
+        <v>4.179453858878548</v>
       </c>
       <c r="G71">
-        <v>-9.998835339699276</v>
+        <v>-9.272813376356584</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.4518824093238</v>
       </c>
       <c r="E72">
-        <v>-16.76555325484568</v>
+        <v>-16.16413918253124</v>
       </c>
       <c r="F72">
-        <v>3.899059776704944</v>
+        <v>3.992643755668815</v>
       </c>
       <c r="G72">
-        <v>-11.76931961639652</v>
+        <v>-9.777532963688968</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.53107453448021</v>
       </c>
       <c r="E73">
-        <v>-18.66576787908316</v>
+        <v>-16.41098529762242</v>
       </c>
       <c r="F73">
-        <v>4.100401100894587</v>
+        <v>4.326127904687841</v>
       </c>
       <c r="G73">
-        <v>-9.480889720268312</v>
+        <v>-9.426506605063127</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.57697622795519</v>
       </c>
       <c r="E74">
-        <v>-17.19149414868613</v>
+        <v>-16.31922009340034</v>
       </c>
       <c r="F74">
-        <v>4.12176303947798</v>
+        <v>4.140008659892042</v>
       </c>
       <c r="G74">
-        <v>-10.6641248569912</v>
+        <v>-9.817468218326933</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.59558160560866</v>
       </c>
       <c r="E75">
-        <v>-17.84465308089661</v>
+        <v>-16.18885078991397</v>
       </c>
       <c r="F75">
-        <v>4.762281566344642</v>
+        <v>4.012423512512862</v>
       </c>
       <c r="G75">
-        <v>-10.26746398828499</v>
+        <v>-9.425135964152792</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.57850196953237</v>
       </c>
       <c r="E76">
-        <v>-16.57544000645166</v>
+        <v>-17.12699477681154</v>
       </c>
       <c r="F76">
-        <v>4.223634005939457</v>
+        <v>4.112180485362395</v>
       </c>
       <c r="G76">
-        <v>-10.18722014253253</v>
+        <v>-8.99223665514964</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.52162243213567</v>
       </c>
       <c r="E77">
-        <v>-17.3338745393239</v>
+        <v>-16.88544400615951</v>
       </c>
       <c r="F77">
-        <v>4.388455924809281</v>
+        <v>4.267603747680055</v>
       </c>
       <c r="G77">
-        <v>-10.14398882284829</v>
+        <v>-9.260225671310531</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.43068959117729</v>
       </c>
       <c r="E78">
-        <v>-17.77068438720141</v>
+        <v>-17.02409065981626</v>
       </c>
       <c r="F78">
-        <v>4.450528807770659</v>
+        <v>3.907987920572317</v>
       </c>
       <c r="G78">
-        <v>-9.709976031277025</v>
+        <v>-9.371169262709889</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.29756417870196</v>
       </c>
       <c r="E79">
-        <v>-19.1885616610186</v>
+        <v>-17.69026160310743</v>
       </c>
       <c r="F79">
-        <v>4.176445228471581</v>
+        <v>3.557563658166042</v>
       </c>
       <c r="G79">
-        <v>-9.910199255458686</v>
+        <v>-9.029106895637636</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.12392918546235</v>
       </c>
       <c r="E80">
-        <v>-19.26561203751682</v>
+        <v>-18.26898668195434</v>
       </c>
       <c r="F80">
-        <v>3.48472199896827</v>
+        <v>3.729471431799412</v>
       </c>
       <c r="G80">
-        <v>-9.523384809977863</v>
+        <v>-8.434137783907351</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.915505549344724</v>
       </c>
       <c r="E81">
-        <v>-21.10514824429855</v>
+        <v>-18.01842344272744</v>
       </c>
       <c r="F81">
-        <v>4.428252351574574</v>
+        <v>3.963394102675965</v>
       </c>
       <c r="G81">
-        <v>-9.005111542100714</v>
+        <v>-8.523998307361175</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.665267148989129</v>
       </c>
       <c r="E82">
-        <v>-19.83405791833478</v>
+        <v>-19.31447456875343</v>
       </c>
       <c r="F82">
-        <v>4.156191645473133</v>
+        <v>3.505651529767403</v>
       </c>
       <c r="G82">
-        <v>-9.021206782504928</v>
+        <v>-8.579117652541054</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.380504628396899</v>
       </c>
       <c r="E83">
-        <v>-19.76378973593001</v>
+        <v>-19.74905414214951</v>
       </c>
       <c r="F83">
-        <v>4.154188653093164</v>
+        <v>3.605314068733017</v>
       </c>
       <c r="G83">
-        <v>-8.950047022557248</v>
+        <v>-8.041222028317097</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.067178301595137</v>
       </c>
       <c r="E84">
-        <v>-21.76924673513864</v>
+        <v>-21.09821653459742</v>
       </c>
       <c r="F84">
-        <v>4.250912144513645</v>
+        <v>3.498694900318692</v>
       </c>
       <c r="G84">
-        <v>-8.775559213182488</v>
+        <v>-7.69122560843245</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.720108695617037</v>
       </c>
       <c r="E85">
-        <v>-23.35443612717655</v>
+        <v>-22.04977124086286</v>
       </c>
       <c r="F85">
-        <v>3.563274423040942</v>
+        <v>3.514508434038135</v>
       </c>
       <c r="G85">
-        <v>-9.379994884800148</v>
+        <v>-7.816312908654166</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.352225212173639</v>
       </c>
       <c r="E86">
-        <v>-23.67249320364324</v>
+        <v>-23.11965093777266</v>
       </c>
       <c r="F86">
-        <v>4.22795477031246</v>
+        <v>3.475613271007087</v>
       </c>
       <c r="G86">
-        <v>-8.190634941266511</v>
+        <v>-7.478554354040362</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.971544044670014</v>
       </c>
       <c r="E87">
-        <v>-24.32028203361072</v>
+        <v>-23.69211297394173</v>
       </c>
       <c r="F87">
-        <v>3.65247799517881</v>
+        <v>3.472311398539528</v>
       </c>
       <c r="G87">
-        <v>-9.217742329951641</v>
+        <v>-6.977870977845838</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.576779414656323</v>
       </c>
       <c r="E88">
-        <v>-27.36954902224322</v>
+        <v>-25.19568761023544</v>
       </c>
       <c r="F88">
-        <v>3.819829748096783</v>
+        <v>3.287580497510822</v>
       </c>
       <c r="G88">
-        <v>-8.389115493433604</v>
+        <v>-7.192771808118738</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.186589864468724</v>
       </c>
       <c r="E89">
-        <v>-28.43394025038726</v>
+        <v>-26.76914002706938</v>
       </c>
       <c r="F89">
-        <v>3.821133598388789</v>
+        <v>3.111512662780592</v>
       </c>
       <c r="G89">
-        <v>-7.8788780974079</v>
+        <v>-6.838916707728425</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.808359490770049</v>
       </c>
       <c r="E90">
-        <v>-28.23373677507956</v>
+        <v>-27.84811110356923</v>
       </c>
       <c r="F90">
-        <v>3.793114899356498</v>
+        <v>3.042660420994703</v>
       </c>
       <c r="G90">
-        <v>-8.688758482389447</v>
+        <v>-6.796116160901714</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.441948283799131</v>
       </c>
       <c r="E91">
-        <v>-31.34706289518621</v>
+        <v>-28.97197631788482</v>
       </c>
       <c r="F91">
-        <v>3.947764466519944</v>
+        <v>3.010953830285149</v>
       </c>
       <c r="G91">
-        <v>-8.416899037372231</v>
+        <v>-7.34298099816844</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.10265259147437</v>
       </c>
       <c r="E92">
-        <v>-31.79614963573992</v>
+        <v>-31.0424933724969</v>
       </c>
       <c r="F92">
-        <v>3.217296836852895</v>
+        <v>2.935951788900876</v>
       </c>
       <c r="G92">
-        <v>-7.997767489970313</v>
+        <v>-6.369387346739656</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.791576665043176</v>
       </c>
       <c r="E93">
-        <v>-33.11951643264931</v>
+        <v>-32.6630432057544</v>
       </c>
       <c r="F93">
-        <v>3.442205213652183</v>
+        <v>2.726222416390486</v>
       </c>
       <c r="G93">
-        <v>-8.337960563915329</v>
+        <v>-6.985102740363223</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.504392342370846</v>
       </c>
       <c r="E94">
-        <v>-34.49463431927173</v>
+        <v>-33.95760540552044</v>
       </c>
       <c r="F94">
-        <v>3.14671496392996</v>
+        <v>2.333708806247969</v>
       </c>
       <c r="G94">
-        <v>-8.332643782555527</v>
+        <v>-6.807371080834003</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.247582360337688</v>
       </c>
       <c r="E95">
-        <v>-35.58537559666615</v>
+        <v>-36.75887168631344</v>
       </c>
       <c r="F95">
-        <v>2.996676089730497</v>
+        <v>2.470980882035486</v>
       </c>
       <c r="G95">
-        <v>-8.235366133718351</v>
+        <v>-7.09107286331651</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.010624939175663</v>
       </c>
       <c r="E96">
-        <v>-39.24542630236191</v>
+        <v>-38.17140585376124</v>
       </c>
       <c r="F96">
-        <v>2.760720605247474</v>
+        <v>1.780523397923653</v>
       </c>
       <c r="G96">
-        <v>-8.162979323812849</v>
+        <v>-6.631895104631506</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.78538748046016</v>
       </c>
       <c r="E97">
-        <v>-43.56019962433194</v>
+        <v>-40.14747888284671</v>
       </c>
       <c r="F97">
-        <v>2.528897017369616</v>
+        <v>1.787256368173608</v>
       </c>
       <c r="G97">
-        <v>-7.54081016956005</v>
+        <v>-7.281868688779661</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.56287290270555</v>
       </c>
       <c r="E98">
-        <v>-42.53334512014169</v>
+        <v>-42.17218809315159</v>
       </c>
       <c r="F98">
-        <v>1.89033012410395</v>
+        <v>1.634662808903911</v>
       </c>
       <c r="G98">
-        <v>-7.516558963053199</v>
+        <v>-7.353899132048476</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.336752366801784</v>
       </c>
       <c r="E99">
-        <v>-44.85309430975106</v>
+        <v>-43.81028939746781</v>
       </c>
       <c r="F99">
-        <v>1.163204128539794</v>
+        <v>1.378761894096282</v>
       </c>
       <c r="G99">
-        <v>-7.491109424779026</v>
+        <v>-6.972414521650411</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.084758226112054</v>
       </c>
       <c r="E100">
-        <v>-47.60140922275816</v>
+        <v>-47.16313952109997</v>
       </c>
       <c r="F100">
-        <v>1.312338425535401</v>
+        <v>1.118190643871669</v>
       </c>
       <c r="G100">
-        <v>-7.144261562871262</v>
+        <v>-7.213451516024946</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.823794992914622</v>
       </c>
       <c r="E101">
-        <v>-49.68055768880606</v>
+        <v>-48.439235505013</v>
       </c>
       <c r="F101">
-        <v>1.890179361236641</v>
+        <v>0.9340942722735072</v>
       </c>
       <c r="G101">
-        <v>-8.201312886644164</v>
+        <v>-7.583459293200477</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.512938048846153</v>
       </c>
       <c r="E102">
-        <v>-51.36483128172323</v>
+        <v>-51.38498162476847</v>
       </c>
       <c r="F102">
-        <v>0.7131927086015603</v>
+        <v>0.5512783593155632</v>
       </c>
       <c r="G102">
-        <v>-8.544735451648387</v>
+        <v>-7.579399585361295</v>
       </c>
     </row>
   </sheetData>
